--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486306_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486306_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5815</v>
+        <v>1.1802</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3007</v>
+        <v>2.9474</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7192</v>
+        <v>-1.7672</v>
       </c>
       <c r="G2" t="n">
         <v>0.7814</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1698</v>
+        <v>0.7685</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2812</v>
+        <v>-0.0721</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8886</v>
+        <v>0.8406</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3698</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7811</v>
+        <v>-0.6772</v>
       </c>
       <c r="E3" t="n">
-        <v>1.008</v>
+        <v>0.5765</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7891</v>
+        <v>-1.2537</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.9168</v>
+        <v>2.2524</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5414</v>
+        <v>1.8157</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3754</v>
+        <v>0.4367</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2373</v>
+        <v>1.8437</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0428</v>
+        <v>1.5361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1945</v>
+        <v>0.3076</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1541</v>
+        <v>0.4087</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5843</v>
+        <v>0.2796</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5698</v>
+        <v>0.1291</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8959</v>
+        <v>-0.0171</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7282</v>
+        <v>-0.1574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1676</v>
+        <v>0.1403</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1952</v>
+        <v>-2.2599</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3642</v>
+        <v>-0.8064</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2206</v>
+        <v>-0.8168</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1437</v>
+        <v>0.0105</v>
       </c>
       <c r="G4" t="n">
         <v>0.0435</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7553</v>
+        <v>-0.1974</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.411</v>
+        <v>-0.0072</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4153</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0075</v>
+        <v>0.7232</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4078</v>
+        <v>-1.635</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2524</v>
+        <v>-1.9168</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8157</v>
+        <v>-0.5414</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4367</v>
+        <v>-1.3754</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8437</v>
+        <v>0.2373</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5361</v>
+        <v>0.0428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3076</v>
+        <v>0.1945</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4087</v>
+        <v>-2.1541</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2796</v>
+        <v>-0.5843</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1291</v>
+        <v>-1.5698</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7553</v>
+        <v>0.7652</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.4434</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0138</v>
+        <v>0.3217</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.2599</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4552</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>A. KELLY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6024</v>
+        <v>-1.4069</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2295</v>
+        <v>1.1768</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3729</v>
+        <v>-2.5837</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6387</v>
+        <v>-1.9417</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.657</v>
+        <v>-1.9497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0183</v>
+        <v>0.008</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6338</v>
+        <v>1.2244</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6721</v>
+        <v>-1.0339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0382</v>
+        <v>2.2583</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0049</v>
+        <v>-3.1661</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0151</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0199</v>
+        <v>-2.2504</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>0.144</v>
+        <v>0.0775</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2091</v>
+        <v>0.1274</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0499</v>
       </c>
       <c r="V6" t="n">
+        <v>-0.1952</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X6" t="n">
         <v>-1.3252</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.5204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. KELLY</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3013</v>
+        <v>-1.5108</v>
       </c>
       <c r="E7" t="n">
-        <v>0.344</v>
+        <v>-0.3845</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6453</v>
+        <v>-1.1263</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9417</v>
+        <v>-0.6387</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9497</v>
+        <v>-0.657</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008</v>
+        <v>0.0183</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2244</v>
+        <v>-0.6338</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0339</v>
+        <v>-0.6721</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2583</v>
+        <v>0.0382</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1661</v>
+        <v>-0.0049</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.0151</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.2504</v>
+        <v>-0.0199</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8169</v>
+        <v>0.2355</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7054</v>
+        <v>0.0541</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1115</v>
+        <v>0.1815</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3252</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8037</v>
+        <v>-1.9307</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6091</v>
+        <v>-2.1368</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1946</v>
+        <v>0.2061</v>
       </c>
       <c r="G8" t="n">
         <v>0.0594</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0583</v>
+        <v>-0.1854</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5804</v>
+        <v>-0.1081</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4779</v>
+        <v>-0.0772</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9347</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0177</v>
+        <v>-3.135</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0418</v>
+        <v>-2.1283</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9759</v>
+        <v>-1.0067</v>
       </c>
       <c r="G9" t="n">
         <v>-6.1207</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8855</v>
+        <v>0.7682</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4506</v>
+        <v>0.3641</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4349</v>
+        <v>0.4041</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4741</v>
+        <v>-3.2631</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7748</v>
+        <v>-0.5945</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6993</v>
+        <v>-2.6685</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1472</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.632</v>
+        <v>-0.4209</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.358</v>
+        <v>-0.3272</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3197</v>
+        <v>-4.4938</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2118</v>
+        <v>-1.4475</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1079</v>
+        <v>-3.0463</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4375</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5994</v>
+        <v>0.2265</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6609</v>
+        <v>0.1034</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0615</v>
+        <v>0.1232</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8544</v>
+        <v>-6.6846</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3432</v>
+        <v>-5.9885</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5112</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8596</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7898</v>
+        <v>0.9596</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4577</v>
+        <v>0.8124</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3321</v>
+        <v>0.1472</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3045</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.3524</v>
+        <v>-23.6401</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.785600000000002</v>
+        <v>-8.073</v>
       </c>
       <c r="F13" t="n">
         <v>-15.5669</v>
@@ -1441,10 +1441,10 @@
         <v>-7.5502</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9295999999999993</v>
+        <v>0.9296000000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.8718</v>
+        <v>-2.871799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>3.8011</v>
@@ -1468,10 +1468,10 @@
         <v>10.8751</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2678</v>
+        <v>2.9802</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2463000000000002</v>
+        <v>1.4663</v>
       </c>
       <c r="U13" t="n">
         <v>1.5141</v>
@@ -1480,7 +1480,7 @@
         <v>-7.3447</v>
       </c>
       <c r="W13" t="n">
-        <v>4.756499999999999</v>
+        <v>4.756500000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-12.1014</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.806</v>
+        <v>12.4021</v>
       </c>
       <c r="E14" t="n">
         <v>9.6143</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1918</v>
+        <v>2.7878</v>
       </c>
       <c r="G14" t="n">
         <v>6.6659</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0324</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1214</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1538</v>
+        <v>0.7498</v>
       </c>
       <c r="V14" t="n">
         <v>3.5851</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.739</v>
+        <v>6.9948</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5975</v>
+        <v>3.635</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1414</v>
+        <v>3.3598</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5809</v>
+        <v>1.4382</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8278</v>
+        <v>1.0342</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7531</v>
+        <v>0.404</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9396</v>
+        <v>0.416</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3171</v>
+        <v>0.3745</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6225</v>
+        <v>0.0415</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3587</v>
+        <v>1.0222</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5107</v>
+        <v>0.6597</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8694</v>
+        <v>0.3626</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6355</v>
+        <v>0.1661</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.0036</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7378</v>
+        <v>0.1625</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5649999999999999</v>
+        <v>3.2154</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7602</v>
+        <v>3.2154</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1573</v>
+        <v>6.75</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1879</v>
+        <v>4.927</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9693</v>
+        <v>1.823</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4382</v>
+        <v>3.5809</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0342</v>
+        <v>1.8278</v>
       </c>
       <c r="I16" t="n">
-        <v>0.404</v>
+        <v>1.7531</v>
       </c>
       <c r="J16" t="n">
-        <v>0.416</v>
+        <v>3.9396</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3745</v>
+        <v>1.3171</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0415</v>
+        <v>2.6225</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0222</v>
+        <v>-0.3587</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6597</v>
+        <v>0.5107</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3626</v>
+        <v>-0.8694</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6714</v>
+        <v>0.6465</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4434</v>
+        <v>0.2271</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.228</v>
+        <v>0.4194</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2154</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>3.2154</v>
+        <v>0.7602</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7925</v>
+        <v>4.6493</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6413</v>
+        <v>2.753</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1513</v>
+        <v>1.8963</v>
       </c>
       <c r="G17" t="n">
         <v>2.7894</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7571</v>
+        <v>0.0997</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.6862</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0408</v>
+        <v>0.7859</v>
       </c>
       <c r="V17" t="n">
         <v>1.3252</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.874</v>
+        <v>2.4607</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5263</v>
+        <v>0.3735</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3477</v>
+        <v>2.0872</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7877999999999999</v>
+        <v>1.4039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1033</v>
+        <v>0.8119</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6845</v>
+        <v>0.5921</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7776</v>
+        <v>1.0152</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2222</v>
+        <v>0.3832</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5554</v>
+        <v>0.6319</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0102</v>
+        <v>0.3888</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1188</v>
+        <v>0.4286</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1291</v>
+        <v>-0.0399</v>
       </c>
       <c r="P18" t="n">
         <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4336</v>
+        <v>-0.3353</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8362</v>
+        <v>-0.6417</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4026</v>
+        <v>0.3064</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6296</v>
+        <v>2.0646</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2617</v>
+        <v>0.4087</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3679</v>
+        <v>1.6559</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4039</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8119</v>
+        <v>0.1033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5921</v>
+        <v>0.6845</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0152</v>
+        <v>0.7776</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3832</v>
+        <v>0.2222</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6319</v>
+        <v>0.5554</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3888</v>
+        <v>0.0102</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4286</v>
+        <v>-0.1188</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0399</v>
+        <v>0.1291</v>
       </c>
       <c r="P19" t="n">
         <v>0.6525</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.7401</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6243</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.09429999999999999</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.6525</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.1664</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.7534999999999999</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.4129</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.7395</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.187</v>
+        <v>0.6068</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1355</v>
+        <v>-0.9119</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9485</v>
+        <v>1.5188</v>
       </c>
       <c r="G20" t="n">
         <v>0.6869</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5259</v>
+        <v>0.268</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6044</v>
+        <v>-0.3809</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0786</v>
+        <v>0.6489</v>
       </c>
       <c r="V20" t="n">
         <v>0.7395</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3649</v>
+        <v>-1.1413</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7913</v>
+        <v>-0.5678</v>
       </c>
       <c r="F21" t="n">
         <v>-0.5735</v>
@@ -2092,10 +2092,10 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.149</v>
+        <v>0.0745</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3305</v>
+        <v>-0.1069</v>
       </c>
       <c r="U21" t="n">
         <v>0.1815</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.123</v>
+        <v>-1.3449</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.244</v>
+        <v>-2.9522</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.879</v>
+        <v>1.6073</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1751</v>
+        <v>2.2674</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4572</v>
+        <v>2.1806</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2821</v>
+        <v>0.0868</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1702</v>
+        <v>1.1981</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3232</v>
+        <v>1.0069</v>
       </c>
       <c r="L22" t="n">
-        <v>0.153</v>
+        <v>0.1912</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0049</v>
+        <v>1.0693</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1339</v>
+        <v>1.1737</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1291</v>
+        <v>-0.1044</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5225</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5942</v>
+        <v>-0.3725</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.399</v>
+        <v>-0.5179</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9932</v>
+        <v>0.1454</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0647</v>
+        <v>-1.4997</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3252</v>
+        <v>-0.3698</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.3899</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3135</v>
+        <v>-2.1654</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1757</v>
+        <v>-1.1322</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8622</v>
+        <v>-1.0331</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2674</v>
+        <v>-2.1751</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1806</v>
+        <v>-2.4572</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0868</v>
+        <v>0.2821</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1981</v>
+        <v>-2.1702</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0069</v>
+        <v>-2.3232</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1912</v>
+        <v>0.153</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0693</v>
+        <v>-0.0049</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1737</v>
+        <v>-0.1339</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1044</v>
+        <v>0.1291</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3411</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.2872</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5997</v>
+        <v>0.8391</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4997</v>
+        <v>-2.0647</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3698</v>
+        <v>1.3252</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6575</v>
+        <v>-2.1989</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9156</v>
+        <v>-0.5803</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7419</v>
+        <v>-1.6186</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0644</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3528</v>
+        <v>0.1057</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0565</v>
+        <v>0.2788</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2963</v>
+        <v>-0.173</v>
       </c>
       <c r="V24" t="n">
         <v>0.9347</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>25.3525</v>
+        <v>29.0778</v>
       </c>
       <c r="E25" t="n">
-        <v>15.5669</v>
+        <v>15.56709999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>9.7857</v>
+        <v>13.5109</v>
       </c>
       <c r="G25" t="n">
         <v>14.9253</v>
@@ -2386,7 +2386,7 @@
         <v>11.3514</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9297000000000001</v>
+        <v>-0.9297000000000002</v>
       </c>
       <c r="N25" t="n">
         <v>2.8717</v>
@@ -2404,16 +2404,16 @@
         <v>15.2253</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.268</v>
+        <v>2.4574</v>
       </c>
       <c r="T25" t="n">
         <v>-1.5141</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2461999999999999</v>
+        <v>3.9716</v>
       </c>
       <c r="V25" t="n">
-        <v>7.344799999999999</v>
+        <v>7.344799999999998</v>
       </c>
       <c r="W25" t="n">
         <v>12.1013</v>
